--- a/analise-marketing/tests/results/modelo.xlsx
+++ b/analise-marketing/tests/results/modelo.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Campanhas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Campanhas!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Campanhas!$A$1:$M$3</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:M3"/>
   <cols>
     <col min="1" max="1" width="38.83203125" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -414,117 +414,137 @@
     <col min="9" max="9" width="21.83203125" customWidth="1"/>
     <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="11" max="11" width="21.83203125" customWidth="1"/>
+    <col min="12" max="12" width="21.83203125" customWidth="1"/>
+    <col min="13" max="13" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>empresas</v>
+      </c>
+      <c r="B1" t="str">
+        <v>colaboradores</v>
+      </c>
+      <c r="C1" t="str">
         <v>campanha</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>data de envio</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>enviados</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>entregues</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>visualização</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>lidos</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>cliques</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>taxa de abertura</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>taxa de cliques</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>canal</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>opt-out</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>EmpA</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Colab1</v>
+      </c>
+      <c r="C2" t="str">
         <v>Boas-vindas setembro</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
         <v>2026-09-24</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>12000</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>11720</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>4680</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>1280</v>
       </c>
-      <c r="H2" s="1">
+      <c r="J2" s="1">
         <v>0.4</v>
       </c>
-      <c r="I2" s="1">
+      <c r="K2" s="1">
         <v>0.109</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>E-mail</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>EmpB</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Colab2</v>
+      </c>
+      <c r="C3" t="str">
         <v>Oferta WhatsApp</v>
       </c>
-      <c r="B3" t="str">
+      <c r="D3" t="str">
         <v>2026-09-25</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>3200</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>3100</v>
       </c>
-      <c r="E3">
+      <c r="G3">
         <v>2650</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <v>570</v>
       </c>
-      <c r="H3" s="1">
+      <c r="J3" s="1">
         <v>0.855</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <v>0.184</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>WhatsApp</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:M3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>